--- a/benchmark/generated_files/CC-1_M_001.xlsx
+++ b/benchmark/generated_files/CC-1_M_001.xlsx
@@ -520,18 +520,18 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - SARA ASSICURAZIONI RCA AUTO</t>
+          <t>Pagam. POS - PAGAMENTO POS 50,11 EUR DEL 03.01.2026 A (ITA) INCOOP</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>48.23</v>
+        <v>50.11</v>
       </c>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="inlineStr">
@@ -542,20 +542,20 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 244,05 EUR DEL 05.01.2026 A (ITA) BAGNO MARINO N.42 RICCIONE</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>244.05</v>
-      </c>
-      <c r="E13" s="3" t="n"/>
+          <t>Bonif. v/fav. - RIF:216654757 ORD. REGIONE LOMBARDIA BONUS</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n">
+        <v>310.41</v>
+      </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -571,11 +571,11 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:218910914 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>Pagam. POS - PAGAMENTO POS 41,59 EUR DEL 08.01.2026 A (ITA) COLOURS &amp; BEAUTY SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>48.36</v>
+        <v>41.59</v>
       </c>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="inlineStr">
@@ -630,18 +630,18 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 93,49 EUR DEL 13.01.2026 A (ITA) MUSEO NAZIONALE SCIENZA</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>93.48999999999999</v>
+        <v>6.75</v>
       </c>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="inlineStr">
@@ -659,13 +659,13 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 46,48 EUR DEL 16.01.2026 A (ITA) STAZIONE Q8</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>46.48</v>
-      </c>
-      <c r="E18" s="3" t="n"/>
+          <t>Bonif. v/fav. - RIF:210481506 ORD. REGIONE LOMBARDIA BONUS</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n">
+        <v>387.71</v>
+      </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -674,20 +674,20 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46038</v>
+        <v>46039</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46038</v>
+        <v>46041</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:210481506 ORD. REGIONE LOMBARDIA BONUS</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n">
-        <v>387.71</v>
-      </c>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1626 CONAD SUPERSTORE</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>38.71</v>
+      </c>
+      <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -696,18 +696,18 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>46040</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 14,58 EUR DEL 17.01.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>Addebito SDD - ENI PLENITUDE GAS E LUCE</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>14.58</v>
+        <v>160.33</v>
       </c>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="inlineStr">
@@ -718,18 +718,18 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - ENEL SERVIZIO ELETTRICO NAZ.</t>
+          <t>Pagam. POS - PAGAMENTO POS 83,46 EUR DEL 20.01.2026 A (ITA) DECATHLON ASSAGO</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>115.39</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="inlineStr">
@@ -747,11 +747,11 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 142,57 EUR DEL 22.01.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4505 SUSHIKO CINISELLO BALSAMO</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>142.57</v>
+        <v>30.58</v>
       </c>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="inlineStr">
@@ -762,20 +762,20 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46047</v>
+        <v>46045</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46047</v>
+        <v>46045</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 2052 ESSELUNGA S.P.A.</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>127.36</v>
-      </c>
-      <c r="E23" s="3" t="n"/>
+          <t>Bonif. v/fav. - RIF:210520596 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n">
+        <v>150.9</v>
+      </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -791,13 +791,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218147720 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n">
-        <v>2098.82</v>
-      </c>
+          <t>Pagam. POS - PAGAMENTO POS 13,01 EUR DEL 27.01.2026 A (ITA) UNIEURO S.P.A.</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -809,16 +809,16 @@
         <v>46049</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
+          <t>Bonif. v/fav. - RIF:217030010 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n">
-        <v>2125.42</v>
+        <v>2144.27</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -835,12 +835,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212815034 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:217273315 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n">
-        <v>2096.5</v>
+        <v>2134.96</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -853,16 +853,16 @@
         <v>46049</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213327421 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:218990305 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n">
-        <v>2142.89</v>
+        <v>2122.13</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -879,12 +879,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217273315 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
         </is>
       </c>
       <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="n">
-        <v>2134.96</v>
+        <v>2105.34</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -901,12 +901,12 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218990305 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:211096280 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n">
-        <v>2122.13</v>
+        <v>2075.25</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -919,16 +919,16 @@
         <v>46049</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
+          <t>Bonif. v/fav. - RIF:214163953 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="n">
-        <v>2105.34</v>
+        <v>2131.11</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211096280 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:217427625 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="n">
-        <v>2075.25</v>
+        <v>2127.57</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -967,12 +967,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214163953 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
         </is>
       </c>
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n">
-        <v>2131.11</v>
+        <v>2144.76</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -985,16 +985,16 @@
         <v>46049</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217427625 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:210547605 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n">
-        <v>2127.57</v>
+        <v>2090.85</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
+          <t>Bonif. v/fav. - RIF:212086308 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n">
-        <v>2144.76</v>
+        <v>2129.26</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:210547605 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:216718473 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n">
-        <v>2090.85</v>
+        <v>2082.98</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -1055,13 +1055,13 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212086308 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n">
-        <v>2129.26</v>
-      </c>
+          <t>GIROCONTO DA CC 0123456 A CC 0468012 ACCANTONAMENTO RISPARMIO</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>444.94</v>
+      </c>
+      <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1070,20 +1070,20 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46049</v>
+        <v>46053</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46049</v>
+        <v>46053</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216718473 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n">
-        <v>2082.98</v>
-      </c>
+          <t>Pagam. POS - PAGAMENTO POS 75,76 EUR DEL 31.01.2026 A (ITA) DECATHLON ASSAGO</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>75.76000000000001</v>
+      </c>
+      <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1092,20 +1092,20 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46049</v>
+        <v>46059</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46050</v>
+        <v>46059</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0123456 A CC 0468012 ACCANTONAMENTO RISPARMIO</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>444.94</v>
-      </c>
-      <c r="E38" s="3" t="n"/>
+          <t>Bonif. v/fav. - RIF:219667820 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n">
+        <v>314.21</v>
+      </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1114,20 +1114,20 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46055</v>
+        <v>46060</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46055</v>
+        <v>46060</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 386,45 EUR DEL 02.02.2026 A (ITA) LIBRERIA FELTRINELLI</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>386.45</v>
-      </c>
-      <c r="E39" s="3" t="n"/>
+          <t>Bonif. v/fav. - RIF:217190929 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n">
+        <v>303.98</v>
+      </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1136,20 +1136,20 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46059</v>
+        <v>46061</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46059</v>
+        <v>46061</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219667820 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n">
-        <v>314.21</v>
-      </c>
+          <t>Disposizione - RIF:215213522 BEN. VERDI ROSA AIUTO NIPOTE</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>796.85</v>
+      </c>
+      <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1158,18 +1158,18 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46061</v>
+        <v>46064</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46061</v>
+        <v>46065</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:215213522 BEN. VERDI ROSA AIUTO NIPOTE</t>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 BEN. SOFIA ROSSI</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>796.85</v>
+        <v>174.59</v>
       </c>
       <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="inlineStr">
@@ -1180,18 +1180,18 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 BEN. SOFIA ROSSI</t>
+          <t>Disposizione - RIF:213971793 BEN. UNIVERSITA' DEGLI STUDI DI BOLOGNA</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>174.59</v>
+        <v>95.69</v>
       </c>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="inlineStr">
@@ -1209,11 +1209,11 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:212592974 BEN. AFFITTO APPARTAMENTO SOFIA BOLOGNA</t>
+          <t>Pagam. POS - PAGAMENTO POS 55,64 EUR DEL 12.02.2026 A (ITA) FLOWER BURGER</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>95.69</v>
+        <v>55.64</v>
       </c>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="inlineStr">
@@ -1231,11 +1231,11 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 168,51 EUR DEL 12.02.2026 A (ITA) LEROY MERLIN ITALIA</t>
+          <t>Addebito SDD - APPLE.COM/BILL</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>168.51</v>
+        <v>10.3</v>
       </c>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="inlineStr">
@@ -1246,18 +1246,18 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46071</v>
+        <v>46067</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46073</v>
+        <v>46067</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
+          <t>Pagam. POS - PAGAMENTO POS 74,04 EUR DEL 14.02.2026 A (ITA) DESPAR</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>7.34</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="inlineStr">
@@ -1268,18 +1268,18 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46072</v>
+        <v>46070</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46072</v>
+        <v>46070</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 161,19 EUR DEL 19.02.2026 A (ITA) BAGNO MARINO N.42 RICCIONE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6143 LA FELTRINELLI CENTRO COMMERCIALE LE GRANGE</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>161.19</v>
+        <v>593.5700000000001</v>
       </c>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="inlineStr">
@@ -1290,18 +1290,18 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:214089126 BEN. RICARICA REVOLUT LAURA</t>
+          <t>Pagam. POS - PAGAMENTO POS 107,76 EUR DEL 20.02.2026 A (ITA) MACELLERIA BONI</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>295.06</v>
+        <v>107.76</v>
       </c>
       <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="inlineStr">
@@ -1312,18 +1312,18 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46078</v>
+        <v>46076</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 201,71 EUR DEL 25.02.2026 A (ITA) AGRITURISMO IL CASALE</t>
+          <t>Disposizione - RIF:214089126 BEN. RICARICA REVOLUT LAURA</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>201.71</v>
+        <v>295.06</v>
       </c>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="inlineStr">
@@ -1337,17 +1337,17 @@
         <v>46080</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO STIPENDIO MESE DI FEBBRAIO 2026</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n">
-        <v>2088.95</v>
-      </c>
+          <t>Pagam. POS - PAGAMENTO POS 151,61 EUR DEL 27.02.2026 A (ITA) LA FELTRINELLI</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>151.61</v>
+      </c>
+      <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1359,16 +1359,16 @@
         <v>46080</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46080</v>
+        <v>46081</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO STIPENDIO MESE DI FEBBRAIO 2026</t>
+          <t>Bonif. v/fav. - RIF:213470105 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="D50" s="3" t="n"/>
       <c r="E50" s="3" t="n">
-        <v>2141.95</v>
+        <v>2104.26</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:215492066 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:216783308 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="D51" s="3" t="n"/>
       <c r="E51" s="3" t="n">
-        <v>2068.17</v>
+        <v>2098.56</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO STIPENDIO MESE DI FEBBRAIO 2026</t>
+          <t>Bonif. v/fav. - RIF:217072684 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="D52" s="3" t="n"/>
       <c r="E52" s="3" t="n">
-        <v>2075.23</v>
+        <v>2082.68</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>46080</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="D53" s="3" t="n"/>
       <c r="E53" s="3" t="n">
-        <v>2135.03</v>
+        <v>2116.95</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -1447,16 +1447,16 @@
         <v>46080</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46080</v>
+        <v>46081</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217307727 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>ACCREDITO STIPENDIO MESE DI FEBBRAIO 2026</t>
         </is>
       </c>
       <c r="D54" s="3" t="n"/>
       <c r="E54" s="3" t="n">
-        <v>2111.59</v>
+        <v>2135.03</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -1469,16 +1469,16 @@
         <v>46080</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218667566 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:217307727 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="D55" s="3" t="n"/>
       <c r="E55" s="3" t="n">
-        <v>2077.97</v>
+        <v>2111.59</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -1491,16 +1491,16 @@
         <v>46080</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46080</v>
+        <v>46081</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:210289293 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:218667566 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="D56" s="3" t="n"/>
       <c r="E56" s="3" t="n">
-        <v>2114.59</v>
+        <v>2077.97</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219233986 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:210289293 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="D57" s="3" t="n"/>
       <c r="E57" s="3" t="n">
-        <v>2097.33</v>
+        <v>2114.59</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO STIPENDIO MESE DI FEBBRAIO 2026</t>
+          <t>Bonif. v/fav. - RIF:219233986 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="D58" s="3" t="n"/>
       <c r="E58" s="3" t="n">
-        <v>2148.05</v>
+        <v>2097.33</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D59" s="3" t="n"/>
       <c r="E59" s="3" t="n">
-        <v>2128.78</v>
+        <v>2148.05</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>46080</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="D60" s="3" t="n"/>
       <c r="E60" s="3" t="n">
-        <v>2058.04</v>
+        <v>2128.78</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D61" s="3" t="n"/>
       <c r="E61" s="3" t="n">
-        <v>2136.49</v>
+        <v>2058.04</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>46080</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46080</v>
+        <v>46081</v>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="D62" s="3" t="n"/>
       <c r="E62" s="3" t="n">
-        <v>2126</v>
+        <v>2136.49</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -1642,20 +1642,20 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 4728 CONAD SUPERSTORE</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="n">
-        <v>87.17</v>
-      </c>
-      <c r="E63" s="3" t="n"/>
+          <t>ACCREDITO STIPENDIO MESE DI FEBBRAIO 2026</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n"/>
+      <c r="E63" s="3" t="n">
+        <v>2126</v>
+      </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1667,15 +1667,15 @@
         <v>46081</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46083</v>
+        <v>46081</v>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:217550917 BEN. CONDOMINIO RESIDENZA MARE</t>
+          <t>Pagam. POS - PAGAMENTO POS 87,17 EUR DEL 28.02.2026 A (ITA) CARREFOUR CONTACT</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>114.44</v>
+        <v>87.17</v>
       </c>
       <c r="E64" s="3" t="n"/>
       <c r="F64" s="3" t="inlineStr">
